--- a/examples/EXAMPLE_student_answers.xlsx
+++ b/examples/EXAMPLE_student_answers.xlsx
@@ -483,10 +483,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -510,10 +508,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -537,10 +533,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -564,10 +558,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -591,10 +583,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -618,10 +608,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -645,10 +633,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -672,10 +658,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -699,10 +683,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -726,10 +708,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -753,10 +733,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -780,10 +758,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Q12</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -807,10 +783,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Q13</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -834,10 +808,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -861,10 +833,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Q15</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -888,10 +858,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Q16</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -915,10 +883,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Q17</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -942,10 +908,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Q18</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -969,10 +933,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Q19</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -996,10 +958,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Q20</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -1049,9 +1009,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -1066,9 +1024,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -1090,9 +1046,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -1142,9 +1096,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
@@ -1201,9 +1153,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
@@ -1225,9 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
@@ -1263,9 +1211,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -1287,9 +1233,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
